--- a/model_coefs.xlsx
+++ b/model_coefs.xlsx
@@ -404,7 +404,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -438,7 +438,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>Cardboard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>Fabric</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PP</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>Rubber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>Styrofoam</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>Stainless Steel</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WO</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nasal Lavage</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
